--- a/education_forms/041_water_cycle_understanding_survey--education_forms.xlsx
+++ b/education_forms/041_water_cycle_understanding_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -736,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First name</t>
+          <t>First Name Error</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Last name</t>
+          <t>Last Name Error</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Error</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Water cycle</t>
+          <t>Water Cycle Error</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Quiz score</t>
+          <t>Quiz Score Error</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Confidence level</t>
+          <t>Confidence Level Error</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Explanation Error</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Water cycle concepts</t>
+          <t>Water Cycle Concepts Error</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Additional Comments Error</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>First name</t>
+          <t>First Name Corrected</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Last name</t>
+          <t>Last Name Corrected</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Corrected</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Water cycle</t>
+          <t>Water Cycle Corrected</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Quiz score</t>
+          <t>Quiz Score Corrected</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Confidence level</t>
+          <t>Confidence Level Corrected</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Explanation Corrected</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
